--- a/templates/TATA Capital/TATA_Collection_and_Repo_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Collection_and_Repo_Agency_Template_2026-27.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-report-generator\templates\TATA Capital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3FD499-75FF-46EB-95F3-6BC093F687AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C68EAD-17AD-4A05-A259-EB63F503E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="2" r:id="rId1"/>
@@ -35,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2855,6 +2853,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3304,7 +3305,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
